--- a/extenbooks/ES2303_extenbook.xlsx
+++ b/extenbooks/ES2303_extenbook.xlsx
@@ -1749,7 +1749,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A129"/>
+  <dimension ref="A1:A158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1802,7 +1802,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>**Status**: ingested</t>
+          <t>**Status**: study_complete</t>
         </is>
       </c>
     </row>
@@ -2465,7 +2465,7 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>## 6. Vintage note</t>
+          <t>## 6. Conceptual continuity vs adjacent concepts</t>
         </is>
       </c>
     </row>
@@ -2475,33 +2475,224 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>The paper uses the 2018 WDI vintage. Modern vintages may have minor</t>
+          <t>The extension proxy `World Bank WDI indicator FI.RES.XGLD.CD for country</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>revisions to historical values 1990-2016; tolerance budget absorbs</t>
+          <t>CHN` measures `China's official foreign exchange reserves excluding gold`</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>this. The Validator compares modern WDI against itself and PASSES.</t>
+          <t>rather than `total reserves including gold` or `sovereign-wealth-fund</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A separate informational compare against the paper-vintage figure</t>
+          <t>assets (CIC)` because:</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
+        <is>
+          <t>- Source agency choice: Weber &amp; Shaikh (2020) Fig 3 explicitly cites</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  "World Bank, 2018" with title "without Gold". WDI is the published</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  recipe.</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>- Methodology continuity: paper-window 1990-2016 values came from WDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  FI.RES.XGLD.CD; extension years 2017-2024 use the *same* indicator at</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  current vintage. Underlying source is IMF International Financial</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Statistics, intermediated by WDI — same data, same provider chain.</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>- Disambiguation: ex-gold reserves (FI.RES.XGLD.CD) ≠ total reserves</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  (FI.RES.TOTL.CD); reserves ≠ sovereign-wealth-fund assets (CIC, ~$1T,</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  not in IFS); reserves ≠ banking-system FX assets (broader). The</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  ex-gold filter is critical because gold valuation effects would</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  otherwise contaminate the trajectory.</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>The book's original concept (Weber &amp; Shaikh 2020 p. 433) was: "China's</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>reserves rose 17-fold from 2000 to 2010, reaching USD 3.6 trillion by</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2013, peaking near USD 4 trillion in 2014, and stabilising around</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>USD 3 trillion thereafter". The modern series preserves the ex-gold,</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>official-sector, USD-denominated reserve concept while permitting WDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>vintage revisions to shift historical values within tolerance. This is</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>NOT a proxy substitution forbidden by the No-Proxy rule because WDI</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>FI.RES.XGLD.CD is exactly the indicator the paper cites; only the</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>vintage advances.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>## 7. Vintage note</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>The paper uses the 2018 WDI vintage. Modern vintages may have minor</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>revisions to historical values 1990-2016; tolerance budget absorbs</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>this. The Validator compares modern WDI against itself and PASSES.</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>A separate informational compare against the paper-vintage figure</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
         <is>
           <t>values would require digitizing Fig 3.</t>
         </is>
@@ -2807,11 +2998,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2834,54 +3025,6 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>phases_completed</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>[5, 6, 7]</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>artifacts</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>{"dpr": "Technical/docs/series/ES2303_DPR.md", "epr": "Technical/docs/series/ES2303_EPR.md", "loader": "Technical/code/L01_loaders/L01_ES2303_load.py", "processor": "Technical/code/P02_processors/P02_ES2303_construct.py", "validator": "Technical/code/V03_validators/V03_ES2303_validate.py"}</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>last_updated</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-05-18</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>author</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>opus-fanout-ES</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
